--- a/data/comRead_vs_refCOM.xlsx
+++ b/data/comRead_vs_refCOM.xlsx
@@ -480,25 +480,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.039</v>
+        <v>0.033</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.93</v>
+        <v>-10.837</v>
       </c>
       <c r="D2" t="n">
-        <v>-35.591</v>
+        <v>-35.774</v>
       </c>
       <c r="E2" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="F2" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-35.518</v>
+        <v>-35.52</v>
       </c>
       <c r="H2" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="I2" t="n">
         <v>7000</v>
@@ -512,25 +512,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109.496</v>
+        <v>105.872</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.93</v>
+        <v>-10.837</v>
       </c>
       <c r="D3" t="n">
-        <v>-27.389</v>
+        <v>-27.802</v>
       </c>
       <c r="E3" t="n">
-        <v>191.103</v>
+        <v>190.96</v>
       </c>
       <c r="F3" t="n">
-        <v>-7</v>
+        <v>-8.875999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-35.518</v>
+        <v>-35.52</v>
       </c>
       <c r="H3" t="n">
-        <v>191.103</v>
+        <v>190.96</v>
       </c>
       <c r="I3" t="n">
         <v>0.01567</v>
@@ -544,25 +544,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>219.665</v>
+        <v>213.148</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.93</v>
+        <v>-10.837</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.133</v>
+        <v>-19.722</v>
       </c>
       <c r="E4" t="n">
-        <v>191.112</v>
+        <v>190.969</v>
       </c>
       <c r="F4" t="n">
-        <v>-7</v>
+        <v>-8.875999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-35.871</v>
+        <v>-35.875</v>
       </c>
       <c r="H4" t="n">
-        <v>191.112</v>
+        <v>190.969</v>
       </c>
       <c r="I4" t="n">
         <v>6000</v>
@@ -576,25 +576,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>315.235</v>
+        <v>308.976</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.93</v>
+        <v>-10.837</v>
       </c>
       <c r="D5" t="n">
-        <v>-11.972</v>
+        <v>-12.505</v>
       </c>
       <c r="E5" t="n">
-        <v>191.796</v>
+        <v>191.885</v>
       </c>
       <c r="F5" t="n">
-        <v>-7</v>
+        <v>-8.365</v>
       </c>
       <c r="G5" t="n">
         <v>-34.137</v>
       </c>
       <c r="H5" t="n">
-        <v>191.796</v>
+        <v>191.885</v>
       </c>
       <c r="I5" t="n">
         <v>0.1567</v>
@@ -608,25 +608,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>411.587</v>
+        <v>404.703</v>
       </c>
       <c r="C6" t="n">
-        <v>-8.93</v>
+        <v>-10.837</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.752</v>
+        <v>-5.295</v>
       </c>
       <c r="E6" t="n">
-        <v>193.377</v>
+        <v>193.575</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.749000000000001</v>
+        <v>-11.127</v>
       </c>
       <c r="G6" t="n">
-        <v>-25.21</v>
+        <v>-27.097</v>
       </c>
       <c r="H6" t="n">
-        <v>193.377</v>
+        <v>193.575</v>
       </c>
     </row>
     <row r="7">
@@ -634,25 +634,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507.128</v>
+        <v>501.106</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.073</v>
+        <v>-10.141</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.345</v>
+        <v>-4.926</v>
       </c>
       <c r="E7" t="n">
-        <v>195.223</v>
+        <v>195.139</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.753</v>
+        <v>-11.232</v>
       </c>
       <c r="G7" t="n">
-        <v>-15.183</v>
+        <v>-17.982</v>
       </c>
       <c r="H7" t="n">
-        <v>195.223</v>
+        <v>195.139</v>
       </c>
     </row>
     <row r="8">
@@ -660,25 +660,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>605.4160000000001</v>
+        <v>597.004</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.452</v>
+        <v>-7.584</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.099</v>
+        <v>-3.572</v>
       </c>
       <c r="E8" t="n">
-        <v>196.421</v>
+        <v>196.827</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.247999999999999</v>
+        <v>-10.655</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.002</v>
+        <v>-7.274</v>
       </c>
       <c r="H8" t="n">
-        <v>196.421</v>
+        <v>196.827</v>
       </c>
     </row>
     <row r="9">
@@ -686,25 +686,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>715.139</v>
+        <v>692.8869999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.526</v>
+        <v>-5.027</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.709</v>
+        <v>-2.218</v>
       </c>
       <c r="E9" t="n">
-        <v>197.217</v>
+        <v>197.157</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.519</v>
+        <v>-10.374</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.48</v>
+        <v>-5.397</v>
       </c>
       <c r="H9" t="n">
-        <v>197.217</v>
+        <v>197.157</v>
       </c>
     </row>
     <row r="10">
@@ -712,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>811.849</v>
+        <v>788.676</v>
       </c>
       <c r="C10" t="n">
-        <v>0.053</v>
+        <v>-2.472</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.483</v>
+        <v>-0.866</v>
       </c>
       <c r="E10" t="n">
-        <v>197.454</v>
+        <v>198.19</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.859</v>
+        <v>-7.395</v>
       </c>
       <c r="G10" t="n">
-        <v>6.075</v>
+        <v>3.101</v>
       </c>
       <c r="H10" t="n">
-        <v>197.454</v>
+        <v>198.19</v>
       </c>
     </row>
     <row r="11">
@@ -738,25 +738,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>907.434</v>
+        <v>884.67</v>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>-2.339</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.418</v>
+        <v>-0.795</v>
       </c>
       <c r="E11" t="n">
-        <v>197.478</v>
+        <v>198.478</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.643000000000001</v>
+        <v>-5.023</v>
       </c>
       <c r="G11" t="n">
-        <v>8.712999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
-        <v>197.478</v>
+        <v>198.478</v>
       </c>
     </row>
     <row r="12">
@@ -764,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1003.219</v>
+        <v>981.516</v>
       </c>
       <c r="C12" t="n">
-        <v>0.42</v>
+        <v>-1.966</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.309</v>
+        <v>-0.598</v>
       </c>
       <c r="E12" t="n">
-        <v>196.594</v>
+        <v>197.886</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.357</v>
+        <v>-2.914</v>
       </c>
       <c r="G12" t="n">
-        <v>7.739</v>
+        <v>4.83</v>
       </c>
       <c r="H12" t="n">
-        <v>196.594</v>
+        <v>197.886</v>
       </c>
     </row>
     <row r="13">
@@ -790,25 +790,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1099.27</v>
+        <v>1076.688</v>
       </c>
       <c r="C13" t="n">
-        <v>0.649</v>
+        <v>-1.6</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2</v>
+        <v>-0.404</v>
       </c>
       <c r="E13" t="n">
-        <v>195.796</v>
+        <v>197.587</v>
       </c>
       <c r="F13" t="n">
-        <v>1.416</v>
+        <v>-0.885</v>
       </c>
       <c r="G13" t="n">
-        <v>10.224</v>
+        <v>10.286</v>
       </c>
       <c r="H13" t="n">
-        <v>195.796</v>
+        <v>197.587</v>
       </c>
     </row>
     <row r="14">
@@ -816,25 +816,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1195.463</v>
+        <v>1173.155</v>
       </c>
       <c r="C14" t="n">
-        <v>0.88</v>
+        <v>-1.229</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09</v>
+        <v>-0.208</v>
       </c>
       <c r="E14" t="n">
-        <v>194.664</v>
+        <v>196.842</v>
       </c>
       <c r="F14" t="n">
-        <v>8.228</v>
+        <v>-1.349</v>
       </c>
       <c r="G14" t="n">
-        <v>12.558</v>
+        <v>10.185</v>
       </c>
       <c r="H14" t="n">
-        <v>194.664</v>
+        <v>196.842</v>
       </c>
     </row>
     <row r="15">
@@ -842,25 +842,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1291.18</v>
+        <v>1268.66</v>
       </c>
       <c r="C15" t="n">
-        <v>1.885</v>
+        <v>-0.861</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.858</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>193.946</v>
+        <v>196.296</v>
       </c>
       <c r="F15" t="n">
-        <v>13.255</v>
+        <v>0.884</v>
       </c>
       <c r="G15" t="n">
-        <v>12.232</v>
+        <v>12.793</v>
       </c>
       <c r="H15" t="n">
-        <v>193.946</v>
+        <v>196.296</v>
       </c>
     </row>
     <row r="16">
@@ -868,25 +868,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1387.315</v>
+        <v>1364.558</v>
       </c>
       <c r="C16" t="n">
-        <v>7.857</v>
+        <v>4.657</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.36</v>
+        <v>-9.868</v>
       </c>
       <c r="E16" t="n">
-        <v>193.707</v>
+        <v>195.918</v>
       </c>
       <c r="F16" t="n">
-        <v>13.395</v>
+        <v>0.649</v>
       </c>
       <c r="G16" t="n">
-        <v>12.497</v>
+        <v>12.475</v>
       </c>
       <c r="H16" t="n">
-        <v>193.707</v>
+        <v>195.918</v>
       </c>
     </row>
     <row r="17">
@@ -894,25 +894,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1483.06</v>
+        <v>1460.747</v>
       </c>
       <c r="C17" t="n">
-        <v>13.805</v>
+        <v>10.583</v>
       </c>
       <c r="D17" t="n">
-        <v>-22.819</v>
+        <v>-20.453</v>
       </c>
       <c r="E17" t="n">
-        <v>193.721</v>
+        <v>194.992</v>
       </c>
       <c r="F17" t="n">
-        <v>13.359</v>
+        <v>2.207</v>
       </c>
       <c r="G17" t="n">
-        <v>7.812</v>
+        <v>12.725</v>
       </c>
       <c r="H17" t="n">
-        <v>193.721</v>
+        <v>194.992</v>
       </c>
     </row>
     <row r="18">
@@ -920,25 +920,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1579.27</v>
+        <v>1556.958</v>
       </c>
       <c r="C18" t="n">
-        <v>19.782</v>
+        <v>16.511</v>
       </c>
       <c r="D18" t="n">
-        <v>-33.329</v>
+        <v>-31.04</v>
       </c>
       <c r="E18" t="n">
-        <v>193.31</v>
+        <v>194.063</v>
       </c>
       <c r="F18" t="n">
-        <v>12.844</v>
+        <v>3.811</v>
       </c>
       <c r="G18" t="n">
-        <v>0.579</v>
+        <v>5.44</v>
       </c>
       <c r="H18" t="n">
-        <v>193.31</v>
+        <v>194.063</v>
       </c>
     </row>
     <row r="19">
@@ -949,22 +949,22 @@
         <v>1500.021</v>
       </c>
       <c r="C19" t="n">
-        <v>-6.888</v>
+        <v>-3.118</v>
       </c>
       <c r="D19" t="n">
-        <v>33.328</v>
+        <v>31.039</v>
       </c>
       <c r="E19" t="n">
-        <v>188.658</v>
+        <v>186.625</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.888</v>
+        <v>-3.118</v>
       </c>
       <c r="G19" t="n">
-        <v>56.195</v>
+        <v>62.617</v>
       </c>
       <c r="H19" t="n">
-        <v>188.658</v>
+        <v>186.625</v>
       </c>
     </row>
     <row r="20">
@@ -972,25 +972,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1600.328</v>
+        <v>1601.058</v>
       </c>
       <c r="C20" t="n">
-        <v>-4.76</v>
+        <v>1.649</v>
       </c>
       <c r="D20" t="n">
-        <v>26.289</v>
+        <v>24.436</v>
       </c>
       <c r="E20" t="n">
-        <v>190.342</v>
+        <v>189.41</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.415</v>
+        <v>3.854</v>
       </c>
       <c r="G20" t="n">
-        <v>53.9</v>
+        <v>57.962</v>
       </c>
       <c r="H20" t="n">
-        <v>190.342</v>
+        <v>189.41</v>
       </c>
     </row>
     <row r="21">
@@ -998,25 +998,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1696.511</v>
+        <v>1699.19</v>
       </c>
       <c r="C21" t="n">
-        <v>-8.359999999999999</v>
+        <v>-4.133</v>
       </c>
       <c r="D21" t="n">
-        <v>19.541</v>
+        <v>18.023</v>
       </c>
       <c r="E21" t="n">
-        <v>188.116</v>
+        <v>186.582</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.357</v>
+        <v>-2.415</v>
       </c>
       <c r="G21" t="n">
-        <v>53.865</v>
+        <v>55.562</v>
       </c>
       <c r="H21" t="n">
-        <v>188.116</v>
+        <v>186.582</v>
       </c>
     </row>
     <row r="22">
@@ -1024,25 +1024,25 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1792.503</v>
+        <v>1809.079</v>
       </c>
       <c r="C22" t="n">
-        <v>-9.298999999999999</v>
+        <v>-4.435</v>
       </c>
       <c r="D22" t="n">
-        <v>12.805</v>
+        <v>10.843</v>
       </c>
       <c r="E22" t="n">
-        <v>187.464</v>
+        <v>186.758</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.526</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>52.573</v>
+        <v>52.501</v>
       </c>
       <c r="H22" t="n">
-        <v>187.464</v>
+        <v>186.758</v>
       </c>
     </row>
     <row r="23">
@@ -1050,25 +1050,25 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1888.097</v>
+        <v>1904.793</v>
       </c>
       <c r="C23" t="n">
-        <v>-8.68</v>
+        <v>-4.819</v>
       </c>
       <c r="D23" t="n">
-        <v>6.098</v>
+        <v>4.588</v>
       </c>
       <c r="E23" t="n">
-        <v>189.469</v>
+        <v>188.578</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.761</v>
+        <v>4.936</v>
       </c>
       <c r="G23" t="n">
-        <v>43.688</v>
+        <v>43.648</v>
       </c>
       <c r="H23" t="n">
-        <v>189.469</v>
+        <v>188.578</v>
       </c>
     </row>
     <row r="24">
@@ -1076,25 +1076,25 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1984.207</v>
+        <v>2001.37</v>
       </c>
       <c r="C24" t="n">
-        <v>-8.441000000000001</v>
+        <v>-4.539</v>
       </c>
       <c r="D24" t="n">
-        <v>5.948</v>
+        <v>4.265</v>
       </c>
       <c r="E24" t="n">
-        <v>191.023</v>
+        <v>191.293</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.441</v>
+        <v>5.428</v>
       </c>
       <c r="G24" t="n">
-        <v>37.297</v>
+        <v>33.96</v>
       </c>
       <c r="H24" t="n">
-        <v>191.023</v>
+        <v>191.293</v>
       </c>
     </row>
     <row r="25">
@@ -1102,25 +1102,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>2080.325</v>
+        <v>2098.831</v>
       </c>
       <c r="C25" t="n">
-        <v>-5.942</v>
+        <v>-3.504</v>
       </c>
       <c r="D25" t="n">
-        <v>4.385</v>
+        <v>3.073</v>
       </c>
       <c r="E25" t="n">
-        <v>193.26</v>
+        <v>192.527</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.104</v>
+        <v>6.236</v>
       </c>
       <c r="G25" t="n">
-        <v>29.851</v>
+        <v>27.137</v>
       </c>
       <c r="H25" t="n">
-        <v>193.26</v>
+        <v>192.527</v>
       </c>
     </row>
     <row r="26">
@@ -1128,25 +1128,25 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2176.658</v>
+        <v>2192.717</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.437</v>
+        <v>-2.507</v>
       </c>
       <c r="D26" t="n">
-        <v>2.819</v>
+        <v>1.924</v>
       </c>
       <c r="E26" t="n">
-        <v>194.495</v>
+        <v>193.75</v>
       </c>
       <c r="F26" t="n">
-        <v>0.855</v>
+        <v>6.95</v>
       </c>
       <c r="G26" t="n">
-        <v>22.515</v>
+        <v>19.814</v>
       </c>
       <c r="H26" t="n">
-        <v>194.495</v>
+        <v>193.75</v>
       </c>
     </row>
     <row r="27">
@@ -1154,25 +1154,25 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>2272.193</v>
+        <v>2288.746</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.953</v>
+        <v>-1.487</v>
       </c>
       <c r="D27" t="n">
-        <v>1.265</v>
+        <v>0.749</v>
       </c>
       <c r="E27" t="n">
-        <v>195.214</v>
+        <v>194.665</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.213</v>
+        <v>5.135</v>
       </c>
       <c r="G27" t="n">
-        <v>19.9</v>
+        <v>17.146</v>
       </c>
       <c r="H27" t="n">
-        <v>195.214</v>
+        <v>194.665</v>
       </c>
     </row>
     <row r="28">
@@ -1180,25 +1180,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2368.353</v>
+        <v>2385.17</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.866</v>
+        <v>-1.433</v>
       </c>
       <c r="D28" t="n">
-        <v>1.21</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>196.005</v>
+        <v>194.546</v>
       </c>
       <c r="F28" t="n">
-        <v>1.875</v>
+        <v>6.198</v>
       </c>
       <c r="G28" t="n">
-        <v>14.796</v>
+        <v>15.215</v>
       </c>
       <c r="H28" t="n">
-        <v>196.005</v>
+        <v>194.546</v>
       </c>
     </row>
     <row r="29">
@@ -1206,25 +1206,25 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>2464.299</v>
+        <v>2481.217</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.409</v>
+        <v>-1.286</v>
       </c>
       <c r="D29" t="n">
-        <v>0.925</v>
+        <v>0.518</v>
       </c>
       <c r="E29" t="n">
-        <v>195.92</v>
+        <v>194.727</v>
       </c>
       <c r="F29" t="n">
-        <v>3.459</v>
+        <v>6.934</v>
       </c>
       <c r="G29" t="n">
-        <v>14.825</v>
+        <v>15.49</v>
       </c>
       <c r="H29" t="n">
-        <v>195.92</v>
+        <v>194.727</v>
       </c>
     </row>
     <row r="30">
@@ -1232,25 +1232,25 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>2560.346</v>
+        <v>2577.085</v>
       </c>
       <c r="C30" t="n">
-        <v>0.048</v>
+        <v>-1.14</v>
       </c>
       <c r="D30" t="n">
-        <v>0.639</v>
+        <v>0.349</v>
       </c>
       <c r="E30" t="n">
-        <v>195.954</v>
+        <v>194.969</v>
       </c>
       <c r="F30" t="n">
-        <v>4.427</v>
+        <v>8.231</v>
       </c>
       <c r="G30" t="n">
-        <v>12.399</v>
+        <v>15.793</v>
       </c>
       <c r="H30" t="n">
-        <v>195.954</v>
+        <v>194.969</v>
       </c>
     </row>
     <row r="31">
@@ -1258,25 +1258,25 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2656.132</v>
+        <v>2672.802</v>
       </c>
       <c r="C31" t="n">
-        <v>0.504</v>
+        <v>-0.993</v>
       </c>
       <c r="D31" t="n">
-        <v>0.354</v>
+        <v>0.18</v>
       </c>
       <c r="E31" t="n">
-        <v>195.668</v>
+        <v>194.915</v>
       </c>
       <c r="F31" t="n">
-        <v>4.49</v>
+        <v>8.721</v>
       </c>
       <c r="G31" t="n">
-        <v>9.747999999999999</v>
+        <v>13.063</v>
       </c>
       <c r="H31" t="n">
-        <v>195.668</v>
+        <v>194.915</v>
       </c>
     </row>
     <row r="32">
@@ -1284,25 +1284,25 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>2752.24</v>
+        <v>2768.716</v>
       </c>
       <c r="C32" t="n">
-        <v>0.962</v>
+        <v>-0.847</v>
       </c>
       <c r="D32" t="n">
-        <v>0.068</v>
+        <v>0.011</v>
       </c>
       <c r="E32" t="n">
-        <v>195.371</v>
+        <v>194.918</v>
       </c>
       <c r="F32" t="n">
-        <v>3.879</v>
+        <v>9.135999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>9.888999999999999</v>
+        <v>10.661</v>
       </c>
       <c r="H32" t="n">
-        <v>195.371</v>
+        <v>194.918</v>
       </c>
     </row>
     <row r="33">
@@ -1310,25 +1310,25 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2848.323</v>
+        <v>2865.571</v>
       </c>
       <c r="C33" t="n">
-        <v>5.499</v>
+        <v>4.729</v>
       </c>
       <c r="D33" t="n">
-        <v>8.083</v>
+        <v>9.978</v>
       </c>
       <c r="E33" t="n">
-        <v>194.678</v>
+        <v>194.773</v>
       </c>
       <c r="F33" t="n">
-        <v>3.891</v>
+        <v>7.175</v>
       </c>
       <c r="G33" t="n">
-        <v>10.583</v>
+        <v>7.992</v>
       </c>
       <c r="H33" t="n">
-        <v>194.678</v>
+        <v>194.773</v>
       </c>
     </row>
     <row r="34">
@@ -1336,25 +1336,25 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2944.805</v>
+        <v>2961.089</v>
       </c>
       <c r="C34" t="n">
-        <v>11.468</v>
+        <v>10.61</v>
       </c>
       <c r="D34" t="n">
-        <v>18.63</v>
+        <v>20.489</v>
       </c>
       <c r="E34" t="n">
-        <v>194.999</v>
+        <v>194.436</v>
       </c>
       <c r="F34" t="n">
-        <v>2.866</v>
+        <v>7.831</v>
       </c>
       <c r="G34" t="n">
-        <v>6.443</v>
+        <v>7.434</v>
       </c>
       <c r="H34" t="n">
-        <v>194.999</v>
+        <v>194.436</v>
       </c>
     </row>
     <row r="35">
@@ -1362,25 +1362,25 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>3040.677</v>
+        <v>3057.134</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4</v>
+        <v>16.524</v>
       </c>
       <c r="D35" t="n">
-        <v>29.109</v>
+        <v>31.059</v>
       </c>
       <c r="E35" t="n">
-        <v>194.246</v>
+        <v>193.501</v>
       </c>
       <c r="F35" t="n">
-        <v>7.48</v>
+        <v>7.022</v>
       </c>
       <c r="G35" t="n">
-        <v>5.193</v>
+        <v>5.887</v>
       </c>
       <c r="H35" t="n">
-        <v>194.246</v>
+        <v>193.501</v>
       </c>
     </row>
     <row r="36">
@@ -1388,25 +1388,25 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>3000.018</v>
+        <v>3000.019</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.62</v>
+        <v>-8.055999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-29.108</v>
+        <v>-31.058</v>
       </c>
       <c r="E36" t="n">
-        <v>189.178</v>
+        <v>189.624</v>
       </c>
       <c r="F36" t="n">
-        <v>-3.62</v>
+        <v>-8.055999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-42.756</v>
+        <v>-42.771</v>
       </c>
       <c r="H36" t="n">
-        <v>189.178</v>
+        <v>189.624</v>
       </c>
     </row>
     <row r="37">
@@ -1414,25 +1414,25 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>3099.017</v>
+        <v>3103.417</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.01</v>
+        <v>-2.645</v>
       </c>
       <c r="D37" t="n">
-        <v>-23.041</v>
+        <v>-24.297</v>
       </c>
       <c r="E37" t="n">
-        <v>190.872</v>
+        <v>192.061</v>
       </c>
       <c r="F37" t="n">
-        <v>1.936</v>
+        <v>-1.565</v>
       </c>
       <c r="G37" t="n">
-        <v>-42.798</v>
+        <v>-40.019</v>
       </c>
       <c r="H37" t="n">
-        <v>190.872</v>
+        <v>192.061</v>
       </c>
     </row>
     <row r="38">
@@ -1440,25 +1440,25 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>3195.088</v>
+        <v>3213.246</v>
       </c>
       <c r="C38" t="n">
-        <v>-5.622</v>
+        <v>-5.128</v>
       </c>
       <c r="D38" t="n">
-        <v>-17.154</v>
+        <v>-17.115</v>
       </c>
       <c r="E38" t="n">
-        <v>191.74</v>
+        <v>190.246</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.382</v>
+        <v>-3.991</v>
       </c>
       <c r="G38" t="n">
-        <v>-35.998</v>
+        <v>-39.003</v>
       </c>
       <c r="H38" t="n">
-        <v>191.74</v>
+        <v>190.246</v>
       </c>
     </row>
     <row r="39">
@@ -1466,25 +1466,25 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>3290.854</v>
+        <v>3309.16</v>
       </c>
       <c r="C39" t="n">
-        <v>-5.639</v>
+        <v>-5.82</v>
       </c>
       <c r="D39" t="n">
-        <v>-11.285</v>
+        <v>-10.844</v>
       </c>
       <c r="E39" t="n">
-        <v>191.731</v>
+        <v>191.247</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.858</v>
+        <v>-4.509</v>
       </c>
       <c r="G39" t="n">
-        <v>-30.13</v>
+        <v>-32.619</v>
       </c>
       <c r="H39" t="n">
-        <v>191.731</v>
+        <v>191.247</v>
       </c>
     </row>
     <row r="40">
@@ -1492,25 +1492,25 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>3387.048</v>
+        <v>3405.38</v>
       </c>
       <c r="C40" t="n">
-        <v>-6.413</v>
+        <v>-6.229</v>
       </c>
       <c r="D40" t="n">
-        <v>-5.39</v>
+        <v>-4.552</v>
       </c>
       <c r="E40" t="n">
-        <v>193.579</v>
+        <v>193.472</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.069</v>
+        <v>-4.509</v>
       </c>
       <c r="G40" t="n">
-        <v>-20.277</v>
+        <v>-22.761</v>
       </c>
       <c r="H40" t="n">
-        <v>193.579</v>
+        <v>193.472</v>
       </c>
     </row>
     <row r="41">
@@ -1518,25 +1518,25 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>3483.14</v>
+        <v>3501.244</v>
       </c>
       <c r="C41" t="n">
-        <v>-6.251</v>
+        <v>-5.852</v>
       </c>
       <c r="D41" t="n">
-        <v>-5.273</v>
+        <v>-4.233</v>
       </c>
       <c r="E41" t="n">
-        <v>194.185</v>
+        <v>195.508</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.527</v>
+        <v>-1.847</v>
       </c>
       <c r="G41" t="n">
-        <v>-13.384</v>
+        <v>-12.96</v>
       </c>
       <c r="H41" t="n">
-        <v>194.185</v>
+        <v>195.508</v>
       </c>
     </row>
     <row r="42">
@@ -1544,25 +1544,25 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>3579.375</v>
+        <v>3598.195</v>
       </c>
       <c r="C42" t="n">
-        <v>-4.33</v>
+        <v>-4.458</v>
       </c>
       <c r="D42" t="n">
-        <v>-3.89</v>
+        <v>-3.057</v>
       </c>
       <c r="E42" t="n">
-        <v>195.448</v>
+        <v>195.786</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.326</v>
+        <v>-0.953</v>
       </c>
       <c r="G42" t="n">
-        <v>-8.401999999999999</v>
+        <v>-5.602</v>
       </c>
       <c r="H42" t="n">
-        <v>195.448</v>
+        <v>195.786</v>
       </c>
     </row>
     <row r="43">
@@ -1570,25 +1570,25 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>3674.847</v>
+        <v>3692.891</v>
       </c>
       <c r="C43" t="n">
-        <v>-2.425</v>
+        <v>-3.096</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.518</v>
+        <v>-1.907</v>
       </c>
       <c r="E43" t="n">
-        <v>196.188</v>
+        <v>196.634</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.179</v>
+        <v>-0.325</v>
       </c>
       <c r="G43" t="n">
-        <v>-3.132</v>
+        <v>-3.063</v>
       </c>
       <c r="H43" t="n">
-        <v>196.188</v>
+        <v>196.634</v>
       </c>
     </row>
     <row r="44">
@@ -1596,25 +1596,25 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>3770.826</v>
+        <v>3789.198</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.51</v>
+        <v>-1.711</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.138</v>
+        <v>-0.738</v>
       </c>
       <c r="E44" t="n">
-        <v>196.508</v>
+        <v>197.44</v>
       </c>
       <c r="F44" t="n">
-        <v>1.298</v>
+        <v>0.204</v>
       </c>
       <c r="G44" t="n">
-        <v>5.356</v>
+        <v>5.4</v>
       </c>
       <c r="H44" t="n">
-        <v>196.508</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="45">
@@ -1622,25 +1622,25 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>3868.543</v>
+        <v>3884.913</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.441</v>
+        <v>-1.639</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.088</v>
+        <v>-0.677</v>
       </c>
       <c r="E45" t="n">
-        <v>196.608</v>
+        <v>197.227</v>
       </c>
       <c r="F45" t="n">
-        <v>2.755</v>
+        <v>0.186</v>
       </c>
       <c r="G45" t="n">
-        <v>11.001</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>196.608</v>
+        <v>197.227</v>
       </c>
     </row>
     <row r="46">
@@ -1648,25 +1648,25 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3962.624</v>
+        <v>3981.541</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.091</v>
+        <v>-1.44</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.836</v>
+        <v>-0.51</v>
       </c>
       <c r="E46" t="n">
-        <v>196.081</v>
+        <v>196.584</v>
       </c>
       <c r="F46" t="n">
-        <v>4.33</v>
+        <v>3.318</v>
       </c>
       <c r="G46" t="n">
-        <v>14.052</v>
+        <v>10.54</v>
       </c>
       <c r="H46" t="n">
-        <v>196.081</v>
+        <v>196.584</v>
       </c>
     </row>
     <row r="47">
@@ -1674,25 +1674,25 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>4059.105</v>
+        <v>4076.876</v>
       </c>
       <c r="C47" t="n">
-        <v>0.267</v>
+        <v>-1.244</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.578</v>
+        <v>-0.344</v>
       </c>
       <c r="E47" t="n">
-        <v>195.521</v>
+        <v>196.857</v>
       </c>
       <c r="F47" t="n">
-        <v>5.31</v>
+        <v>3.774</v>
       </c>
       <c r="G47" t="n">
-        <v>14.033</v>
+        <v>14.164</v>
       </c>
       <c r="H47" t="n">
-        <v>195.521</v>
+        <v>196.857</v>
       </c>
     </row>
     <row r="48">
@@ -1700,25 +1700,25 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>4154.874</v>
+        <v>4173.152</v>
       </c>
       <c r="C48" t="n">
-        <v>0.623</v>
+        <v>-1.046</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.322</v>
+        <v>-0.177</v>
       </c>
       <c r="E48" t="n">
-        <v>195.308</v>
+        <v>196.136</v>
       </c>
       <c r="F48" t="n">
-        <v>5.359</v>
+        <v>3.765</v>
       </c>
       <c r="G48" t="n">
-        <v>10.841</v>
+        <v>14.096</v>
       </c>
       <c r="H48" t="n">
-        <v>195.308</v>
+        <v>196.136</v>
       </c>
     </row>
     <row r="49">
@@ -1726,25 +1726,25 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>4250.641</v>
+        <v>4269.162</v>
       </c>
       <c r="C49" t="n">
-        <v>0.979</v>
+        <v>-0.849</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.065</v>
+        <v>-0.01</v>
       </c>
       <c r="E49" t="n">
-        <v>195.026</v>
+        <v>195.764</v>
       </c>
       <c r="F49" t="n">
-        <v>5.118</v>
+        <v>4.025</v>
       </c>
       <c r="G49" t="n">
-        <v>10.628</v>
+        <v>13.795</v>
       </c>
       <c r="H49" t="n">
-        <v>195.026</v>
+        <v>195.764</v>
       </c>
     </row>
     <row r="50">
@@ -1752,25 +1752,25 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4346.513</v>
+        <v>4365.225</v>
       </c>
       <c r="C50" t="n">
-        <v>5.4</v>
+        <v>4.707</v>
       </c>
       <c r="D50" t="n">
-        <v>-7.883</v>
+        <v>-9.939</v>
       </c>
       <c r="E50" t="n">
-        <v>195.004</v>
+        <v>195.159</v>
       </c>
       <c r="F50" t="n">
-        <v>4.739</v>
+        <v>6.673</v>
       </c>
       <c r="G50" t="n">
-        <v>8.074999999999999</v>
+        <v>13.793</v>
       </c>
       <c r="H50" t="n">
-        <v>195.004</v>
+        <v>195.159</v>
       </c>
     </row>
     <row r="51">
@@ -1778,25 +1778,25 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>4442.463</v>
+        <v>4461.169</v>
       </c>
       <c r="C51" t="n">
-        <v>11.331</v>
+        <v>10.614</v>
       </c>
       <c r="D51" t="n">
-        <v>-18.372</v>
+        <v>-20.498</v>
       </c>
       <c r="E51" t="n">
-        <v>194.827</v>
+        <v>194.319</v>
       </c>
       <c r="F51" t="n">
-        <v>7.319</v>
+        <v>6.8</v>
       </c>
       <c r="G51" t="n">
-        <v>5.489</v>
+        <v>7.72</v>
       </c>
       <c r="H51" t="n">
-        <v>194.827</v>
+        <v>194.319</v>
       </c>
     </row>
     <row r="52">
@@ -1804,25 +1804,25 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>4538.647</v>
+        <v>4556.994</v>
       </c>
       <c r="C52" t="n">
-        <v>17.277</v>
+        <v>16.515</v>
       </c>
       <c r="D52" t="n">
-        <v>-28.887</v>
+        <v>-31.043</v>
       </c>
       <c r="E52" t="n">
-        <v>193.765</v>
+        <v>193.903</v>
       </c>
       <c r="F52" t="n">
-        <v>8.178000000000001</v>
+        <v>8.746</v>
       </c>
       <c r="G52" t="n">
-        <v>3.365</v>
+        <v>3.784</v>
       </c>
       <c r="H52" t="n">
-        <v>193.765</v>
+        <v>193.903</v>
       </c>
     </row>
     <row r="53">
@@ -1830,25 +1830,25 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>4500.019</v>
+        <v>4500.021</v>
       </c>
       <c r="C53" t="n">
-        <v>-6.702</v>
+        <v>-7.223</v>
       </c>
       <c r="D53" t="n">
-        <v>28.886</v>
+        <v>31.042</v>
       </c>
       <c r="E53" t="n">
-        <v>186.191</v>
+        <v>187.126</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.702</v>
+        <v>-7.223</v>
       </c>
       <c r="G53" t="n">
-        <v>63.216</v>
+        <v>58.847</v>
       </c>
       <c r="H53" t="n">
-        <v>186.191</v>
+        <v>187.126</v>
       </c>
     </row>
     <row r="54">
@@ -1856,25 +1856,25 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>4601.692</v>
+        <v>4600.869</v>
       </c>
       <c r="C54" t="n">
-        <v>-2.576</v>
+        <v>-1.469</v>
       </c>
       <c r="D54" t="n">
-        <v>22.703</v>
+        <v>24.451</v>
       </c>
       <c r="E54" t="n">
-        <v>189.346</v>
+        <v>190.627</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.295</v>
+        <v>-0.108</v>
       </c>
       <c r="G54" t="n">
-        <v>58.306</v>
+        <v>53.941</v>
       </c>
       <c r="H54" t="n">
-        <v>189.346</v>
+        <v>190.627</v>
       </c>
     </row>
     <row r="55">
@@ -1882,25 +1882,25 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>4700.516</v>
+        <v>4696.707</v>
       </c>
       <c r="C55" t="n">
-        <v>-6.6</v>
+        <v>-6.372</v>
       </c>
       <c r="D55" t="n">
-        <v>16.693</v>
+        <v>18.187</v>
       </c>
       <c r="E55" t="n">
-        <v>187.312</v>
+        <v>187.349</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.105</v>
+        <v>-6.271</v>
       </c>
       <c r="G55" t="n">
-        <v>56.015</v>
+        <v>53.764</v>
       </c>
       <c r="H55" t="n">
-        <v>187.312</v>
+        <v>187.349</v>
       </c>
     </row>
     <row r="56">
@@ -1908,25 +1908,25 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>4809.865</v>
+        <v>4792.916</v>
       </c>
       <c r="C56" t="n">
-        <v>-6.166</v>
+        <v>-5.709</v>
       </c>
       <c r="D56" t="n">
-        <v>10.043</v>
+        <v>11.9</v>
       </c>
       <c r="E56" t="n">
-        <v>187.683</v>
+        <v>186.878</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.08</v>
+        <v>-4.413</v>
       </c>
       <c r="G56" t="n">
-        <v>50.695</v>
+        <v>50.845</v>
       </c>
       <c r="H56" t="n">
-        <v>187.683</v>
+        <v>186.878</v>
       </c>
     </row>
     <row r="57">
@@ -1934,25 +1934,25 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>4905.709</v>
+        <v>4888.624</v>
       </c>
       <c r="C57" t="n">
-        <v>-6.327</v>
+        <v>-5.63</v>
       </c>
       <c r="D57" t="n">
-        <v>4.214</v>
+        <v>5.645</v>
       </c>
       <c r="E57" t="n">
-        <v>189.267</v>
+        <v>190.067</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.763</v>
+        <v>-1.65</v>
       </c>
       <c r="G57" t="n">
-        <v>41.785</v>
+        <v>40.915</v>
       </c>
       <c r="H57" t="n">
-        <v>189.267</v>
+        <v>190.067</v>
       </c>
     </row>
     <row r="58">
@@ -1960,25 +1960,25 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>5001.71</v>
+        <v>4984.435</v>
       </c>
       <c r="C58" t="n">
-        <v>-5.8</v>
+        <v>-5.509</v>
       </c>
       <c r="D58" t="n">
-        <v>3.914</v>
+        <v>5.503</v>
       </c>
       <c r="E58" t="n">
-        <v>191.414</v>
+        <v>191.922</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.485</v>
+        <v>1.326</v>
       </c>
       <c r="G58" t="n">
-        <v>35.166</v>
+        <v>31.718</v>
       </c>
       <c r="H58" t="n">
-        <v>191.414</v>
+        <v>191.922</v>
       </c>
     </row>
     <row r="59">
@@ -1986,25 +1986,25 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>5097.777</v>
+        <v>5080.455</v>
       </c>
       <c r="C59" t="n">
-        <v>-3.905</v>
+        <v>-4.282</v>
       </c>
       <c r="D59" t="n">
-        <v>2.834</v>
+        <v>4.058</v>
       </c>
       <c r="E59" t="n">
-        <v>193.081</v>
+        <v>192.588</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.439</v>
+        <v>1.737</v>
       </c>
       <c r="G59" t="n">
-        <v>28.224</v>
+        <v>24.579</v>
       </c>
       <c r="H59" t="n">
-        <v>193.081</v>
+        <v>192.588</v>
       </c>
     </row>
     <row r="60">
@@ -2012,25 +2012,25 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>5193.505</v>
+        <v>5176.679</v>
       </c>
       <c r="C60" t="n">
-        <v>-2.017</v>
+        <v>-3.052</v>
       </c>
       <c r="D60" t="n">
-        <v>1.759</v>
+        <v>2.609</v>
       </c>
       <c r="E60" t="n">
-        <v>194.72</v>
+        <v>193.434</v>
       </c>
       <c r="F60" t="n">
-        <v>0.792</v>
+        <v>2.598</v>
       </c>
       <c r="G60" t="n">
-        <v>20.294</v>
+        <v>22.006</v>
       </c>
       <c r="H60" t="n">
-        <v>194.72</v>
+        <v>193.434</v>
       </c>
     </row>
     <row r="61">
@@ -2038,25 +2038,25 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>5289.803</v>
+        <v>5272.488</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.117</v>
+        <v>-1.828</v>
       </c>
       <c r="D61" t="n">
-        <v>0.676</v>
+        <v>1.167</v>
       </c>
       <c r="E61" t="n">
-        <v>194.75</v>
+        <v>194.729</v>
       </c>
       <c r="F61" t="n">
-        <v>2.84</v>
+        <v>3.927</v>
       </c>
       <c r="G61" t="n">
-        <v>15.569</v>
+        <v>19.643</v>
       </c>
       <c r="H61" t="n">
-        <v>194.75</v>
+        <v>194.729</v>
       </c>
     </row>
     <row r="62">
@@ -2064,25 +2064,25 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>5385.751</v>
+        <v>5368.354</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.017</v>
+        <v>-1.785</v>
       </c>
       <c r="D62" t="n">
-        <v>0.619</v>
+        <v>1.117</v>
       </c>
       <c r="E62" t="n">
-        <v>194.911</v>
+        <v>195.315</v>
       </c>
       <c r="F62" t="n">
-        <v>4.968</v>
+        <v>1.21</v>
       </c>
       <c r="G62" t="n">
-        <v>15.851</v>
+        <v>17.004</v>
       </c>
       <c r="H62" t="n">
-        <v>194.911</v>
+        <v>195.315</v>
       </c>
     </row>
     <row r="63">
@@ -2090,25 +2090,25 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>5481.619</v>
+        <v>5464.406</v>
       </c>
       <c r="C63" t="n">
-        <v>0.251</v>
+        <v>-1.561</v>
       </c>
       <c r="D63" t="n">
-        <v>0.467</v>
+        <v>0.853</v>
       </c>
       <c r="E63" t="n">
-        <v>195.113</v>
+        <v>195.086</v>
       </c>
       <c r="F63" t="n">
-        <v>6.875</v>
+        <v>1.97</v>
       </c>
       <c r="G63" t="n">
-        <v>13.369</v>
+        <v>15.105</v>
       </c>
       <c r="H63" t="n">
-        <v>195.113</v>
+        <v>195.086</v>
       </c>
     </row>
     <row r="64">
@@ -2116,25 +2116,25 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>5577.907999999999</v>
+        <v>5560.882</v>
       </c>
       <c r="C64" t="n">
-        <v>0.52</v>
+        <v>-1.336</v>
       </c>
       <c r="D64" t="n">
-        <v>0.313</v>
+        <v>0.588</v>
       </c>
       <c r="E64" t="n">
-        <v>194.735</v>
+        <v>195.116</v>
       </c>
       <c r="F64" t="n">
-        <v>7.821</v>
+        <v>2.266</v>
       </c>
       <c r="G64" t="n">
-        <v>13.533</v>
+        <v>15.094</v>
       </c>
       <c r="H64" t="n">
-        <v>194.735</v>
+        <v>195.116</v>
       </c>
     </row>
     <row r="65">
@@ -2142,25 +2142,25 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>5673.814</v>
+        <v>5657.005</v>
       </c>
       <c r="C65" t="n">
-        <v>0.787</v>
+        <v>-1.112</v>
       </c>
       <c r="D65" t="n">
-        <v>0.161</v>
+        <v>0.324</v>
       </c>
       <c r="E65" t="n">
-        <v>194.708</v>
+        <v>195.116</v>
       </c>
       <c r="F65" t="n">
-        <v>8.026999999999999</v>
+        <v>2.781</v>
       </c>
       <c r="G65" t="n">
-        <v>8.407999999999999</v>
+        <v>12.678</v>
       </c>
       <c r="H65" t="n">
-        <v>194.708</v>
+        <v>195.116</v>
       </c>
     </row>
     <row r="66">
@@ -2168,25 +2168,25 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>5769.559</v>
+        <v>5753.076</v>
       </c>
       <c r="C66" t="n">
-        <v>1.055</v>
+        <v>-0.888</v>
       </c>
       <c r="D66" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="E66" t="n">
-        <v>194.736</v>
+        <v>194.816</v>
       </c>
       <c r="F66" t="n">
-        <v>8.345000000000001</v>
+        <v>5.956</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.386</v>
+        <v>10.009</v>
       </c>
       <c r="H66" t="n">
-        <v>194.736</v>
+        <v>194.816</v>
       </c>
     </row>
     <row r="67">
@@ -2194,25 +2194,25 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>5866.198</v>
+        <v>5852.898999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>6.671</v>
+        <v>3.918</v>
       </c>
       <c r="D67" t="n">
-        <v>9.994</v>
+        <v>8.621</v>
       </c>
       <c r="E67" t="n">
-        <v>194.362</v>
+        <v>194.622</v>
       </c>
       <c r="F67" t="n">
-        <v>7.839</v>
+        <v>6.184</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.637</v>
+        <v>7.309</v>
       </c>
       <c r="H67" t="n">
-        <v>194.362</v>
+        <v>194.622</v>
       </c>
     </row>
     <row r="68">
@@ -2220,25 +2220,25 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>5962.245</v>
+        <v>5961.43</v>
       </c>
       <c r="C68" t="n">
-        <v>12.586</v>
+        <v>10.614</v>
       </c>
       <c r="D68" t="n">
-        <v>20.511</v>
+        <v>20.548</v>
       </c>
       <c r="E68" t="n">
-        <v>193.511</v>
+        <v>194.066</v>
       </c>
       <c r="F68" t="n">
-        <v>6.986</v>
+        <v>6.317</v>
       </c>
       <c r="G68" t="n">
-        <v>0.995</v>
+        <v>6.796</v>
       </c>
       <c r="H68" t="n">
-        <v>193.511</v>
+        <v>194.066</v>
       </c>
     </row>
     <row r="69">
@@ -2246,25 +2246,25 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>6057.825</v>
+        <v>6057.863</v>
       </c>
       <c r="C69" t="n">
-        <v>18.473</v>
+        <v>16.563</v>
       </c>
       <c r="D69" t="n">
-        <v>30.976</v>
+        <v>31.145</v>
       </c>
       <c r="E69" t="n">
-        <v>192.751</v>
+        <v>192.835</v>
       </c>
       <c r="F69" t="n">
-        <v>8.672000000000001</v>
+        <v>6.057</v>
       </c>
       <c r="G69" t="n">
-        <v>4.986</v>
+        <v>11.255</v>
       </c>
       <c r="H69" t="n">
-        <v>192.751</v>
+        <v>192.835</v>
       </c>
     </row>
     <row r="70">
@@ -2275,22 +2275,22 @@
         <v>6000.02</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.078</v>
+        <v>-3.225</v>
       </c>
       <c r="D70" t="n">
-        <v>-30.975</v>
+        <v>-31.144</v>
       </c>
       <c r="E70" t="n">
-        <v>189.292</v>
+        <v>189.611</v>
       </c>
       <c r="F70" t="n">
-        <v>-7.078</v>
+        <v>-3.225</v>
       </c>
       <c r="G70" t="n">
-        <v>-36.071</v>
+        <v>-37.766</v>
       </c>
       <c r="H70" t="n">
-        <v>189.292</v>
+        <v>189.611</v>
       </c>
     </row>
     <row r="71">
@@ -2298,25 +2298,25 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>6101.635</v>
+        <v>6099.469</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.396</v>
+        <v>1.71</v>
       </c>
       <c r="D71" t="n">
-        <v>-24.348</v>
+        <v>-24.623</v>
       </c>
       <c r="E71" t="n">
-        <v>191.201</v>
+        <v>191.75</v>
       </c>
       <c r="F71" t="n">
-        <v>0.53</v>
+        <v>3.901</v>
       </c>
       <c r="G71" t="n">
-        <v>-34.49</v>
+        <v>-37.757</v>
       </c>
       <c r="H71" t="n">
-        <v>191.201</v>
+        <v>191.75</v>
       </c>
     </row>
     <row r="72">
@@ -2324,25 +2324,25 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>6197.61</v>
+        <v>6195.978</v>
       </c>
       <c r="C72" t="n">
-        <v>-5.669</v>
+        <v>-1.917</v>
       </c>
       <c r="D72" t="n">
-        <v>-18.089</v>
+        <v>-18.295</v>
       </c>
       <c r="E72" t="n">
-        <v>191.904</v>
+        <v>190.652</v>
       </c>
       <c r="F72" t="n">
-        <v>-3.671</v>
+        <v>1.347</v>
       </c>
       <c r="G72" t="n">
-        <v>-34.595</v>
+        <v>-38.448</v>
       </c>
       <c r="H72" t="n">
-        <v>191.904</v>
+        <v>190.652</v>
       </c>
     </row>
     <row r="73">
@@ -2350,25 +2350,25 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>6293.385</v>
+        <v>6292.21</v>
       </c>
       <c r="C73" t="n">
-        <v>-6.468</v>
+        <v>-3.022</v>
       </c>
       <c r="D73" t="n">
-        <v>-11.844</v>
+        <v>-11.985</v>
       </c>
       <c r="E73" t="n">
-        <v>192.464</v>
+        <v>191.34</v>
       </c>
       <c r="F73" t="n">
-        <v>-3.23</v>
+        <v>2.639</v>
       </c>
       <c r="G73" t="n">
-        <v>-29.962</v>
+        <v>-31.693</v>
       </c>
       <c r="H73" t="n">
-        <v>192.464</v>
+        <v>191.34</v>
       </c>
     </row>
     <row r="74">
@@ -2376,25 +2376,25 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>6389.808</v>
+        <v>6388.689</v>
       </c>
       <c r="C74" t="n">
-        <v>-6.847</v>
+        <v>-4.397</v>
       </c>
       <c r="D74" t="n">
-        <v>-5.556</v>
+        <v>-5.659</v>
       </c>
       <c r="E74" t="n">
-        <v>193.101</v>
+        <v>192.328</v>
       </c>
       <c r="F74" t="n">
-        <v>0.591</v>
+        <v>5.359</v>
       </c>
       <c r="G74" t="n">
-        <v>-25.762</v>
+        <v>-25.244</v>
       </c>
       <c r="H74" t="n">
-        <v>193.101</v>
+        <v>192.328</v>
       </c>
     </row>
     <row r="75">
@@ -2402,25 +2402,25 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>6485.754</v>
+        <v>6484.272</v>
       </c>
       <c r="C75" t="n">
-        <v>-6.62</v>
+        <v>-4.309</v>
       </c>
       <c r="D75" t="n">
-        <v>-5.397</v>
+        <v>-5.519</v>
       </c>
       <c r="E75" t="n">
-        <v>194.062</v>
+        <v>194.108</v>
       </c>
       <c r="F75" t="n">
-        <v>1.366</v>
+        <v>5.947</v>
       </c>
       <c r="G75" t="n">
-        <v>-16.449</v>
+        <v>-15.648</v>
       </c>
       <c r="H75" t="n">
-        <v>194.062</v>
+        <v>194.108</v>
       </c>
     </row>
     <row r="76">
@@ -2428,25 +2428,25 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>6581.8</v>
+        <v>6580.746</v>
       </c>
       <c r="C76" t="n">
-        <v>-4.592</v>
+        <v>-3.393</v>
       </c>
       <c r="D76" t="n">
-        <v>-3.974</v>
+        <v>-4.063</v>
       </c>
       <c r="E76" t="n">
-        <v>195.432</v>
+        <v>194.61</v>
       </c>
       <c r="F76" t="n">
-        <v>1.621</v>
+        <v>6.886</v>
       </c>
       <c r="G76" t="n">
-        <v>-8.677</v>
+        <v>-8.686</v>
       </c>
       <c r="H76" t="n">
-        <v>195.432</v>
+        <v>194.61</v>
       </c>
     </row>
     <row r="77">
@@ -2454,25 +2454,25 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>6677.817</v>
+        <v>6679.281</v>
       </c>
       <c r="C77" t="n">
-        <v>-2.565</v>
+        <v>-2.458</v>
       </c>
       <c r="D77" t="n">
-        <v>-2.551</v>
+        <v>-2.576</v>
       </c>
       <c r="E77" t="n">
-        <v>195.563</v>
+        <v>195.454</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.027</v>
+        <v>7.734</v>
       </c>
       <c r="G77" t="n">
-        <v>-4.119</v>
+        <v>-6.202</v>
       </c>
       <c r="H77" t="n">
-        <v>195.563</v>
+        <v>195.454</v>
       </c>
     </row>
     <row r="78">
@@ -2480,25 +2480,25 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>6773.871</v>
+        <v>6789.729</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.537</v>
+        <v>-1.409</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.128</v>
+        <v>-0.91</v>
       </c>
       <c r="E78" t="n">
-        <v>196.041</v>
+        <v>196.474</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.987</v>
+        <v>5.791</v>
       </c>
       <c r="G78" t="n">
-        <v>6.946</v>
+        <v>2.176</v>
       </c>
       <c r="H78" t="n">
-        <v>196.041</v>
+        <v>196.474</v>
       </c>
     </row>
     <row r="79">
@@ -2506,25 +2506,25 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>6869.974</v>
+        <v>6885.315000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.461</v>
+        <v>-1.361</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.075</v>
+        <v>-0.834</v>
       </c>
       <c r="E79" t="n">
-        <v>195.672</v>
+        <v>196.702</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.21</v>
+        <v>3.422</v>
       </c>
       <c r="G79" t="n">
-        <v>12.634</v>
+        <v>4.949</v>
       </c>
       <c r="H79" t="n">
-        <v>195.672</v>
+        <v>196.702</v>
       </c>
     </row>
     <row r="80">
@@ -2532,25 +2532,25 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>6965.929</v>
+        <v>6984.191</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.099</v>
+        <v>-1.228</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.82</v>
+        <v>-0.623</v>
       </c>
       <c r="E80" t="n">
-        <v>195.732</v>
+        <v>196.107</v>
       </c>
       <c r="F80" t="n">
-        <v>0.415</v>
+        <v>3.842</v>
       </c>
       <c r="G80" t="n">
-        <v>12.66</v>
+        <v>7.127</v>
       </c>
       <c r="H80" t="n">
-        <v>195.732</v>
+        <v>196.107</v>
       </c>
     </row>
     <row r="81">
@@ -2558,25 +2558,25 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>7061.891</v>
+        <v>7094.082</v>
       </c>
       <c r="C81" t="n">
-        <v>0.264</v>
+        <v>-1.08</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.387</v>
       </c>
       <c r="E81" t="n">
-        <v>195.216</v>
+        <v>195.682</v>
       </c>
       <c r="F81" t="n">
-        <v>4.299</v>
+        <v>4.607</v>
       </c>
       <c r="G81" t="n">
-        <v>12.68</v>
+        <v>12.8</v>
       </c>
       <c r="H81" t="n">
-        <v>195.216</v>
+        <v>195.682</v>
       </c>
     </row>
     <row r="82">
@@ -2584,25 +2584,25 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>7158.152</v>
+        <v>7190.309999999999</v>
       </c>
       <c r="C82" t="n">
-        <v>0.628</v>
+        <v>-0.951</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.31</v>
+        <v>-0.181</v>
       </c>
       <c r="E82" t="n">
-        <v>194.568</v>
+        <v>195.959</v>
       </c>
       <c r="F82" t="n">
-        <v>4.345</v>
+        <v>4.899</v>
       </c>
       <c r="G82" t="n">
-        <v>12.601</v>
+        <v>13.355</v>
       </c>
       <c r="H82" t="n">
-        <v>194.568</v>
+        <v>195.959</v>
       </c>
     </row>
     <row r="83">
@@ -2610,25 +2610,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>7253.738</v>
+        <v>7286.145</v>
       </c>
       <c r="C83" t="n">
-        <v>0.99</v>
+        <v>-0.261</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.056</v>
+        <v>-1.402</v>
       </c>
       <c r="E83" t="n">
-        <v>193.946</v>
+        <v>194.542</v>
       </c>
       <c r="F83" t="n">
-        <v>6.323</v>
+        <v>5.536</v>
       </c>
       <c r="G83" t="n">
-        <v>12.249</v>
+        <v>15.329</v>
       </c>
       <c r="H83" t="n">
-        <v>193.946</v>
+        <v>194.542</v>
       </c>
     </row>
     <row r="84">
@@ -2636,25 +2636,25 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>7349.672</v>
+        <v>7382.434</v>
       </c>
       <c r="C84" t="n">
-        <v>5.604</v>
+        <v>5.698</v>
       </c>
       <c r="D84" t="n">
-        <v>-8.221</v>
+        <v>-11.948</v>
       </c>
       <c r="E84" t="n">
-        <v>193.903</v>
+        <v>194.308</v>
       </c>
       <c r="F84" t="n">
-        <v>6.35</v>
+        <v>5.795</v>
       </c>
       <c r="G84" t="n">
-        <v>12.215</v>
+        <v>12.535</v>
       </c>
       <c r="H84" t="n">
-        <v>193.903</v>
+        <v>194.308</v>
       </c>
     </row>
     <row r="85">
@@ -2662,25 +2662,25 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>7446.102</v>
+        <v>7478.334</v>
       </c>
       <c r="C85" t="n">
-        <v>11.561</v>
+        <v>11.633</v>
       </c>
       <c r="D85" t="n">
-        <v>-18.766</v>
+        <v>-22.451</v>
       </c>
       <c r="E85" t="n">
-        <v>193.565</v>
+        <v>193.65</v>
       </c>
       <c r="F85" t="n">
-        <v>5.518</v>
+        <v>5.606</v>
       </c>
       <c r="G85" t="n">
-        <v>7.022</v>
+        <v>12.908</v>
       </c>
       <c r="H85" t="n">
-        <v>193.565</v>
+        <v>193.65</v>
       </c>
     </row>
     <row r="86">
@@ -2688,25 +2688,25 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>7541.751</v>
+        <v>7574.556</v>
       </c>
       <c r="C86" t="n">
-        <v>17.471</v>
+        <v>17.588</v>
       </c>
       <c r="D86" t="n">
-        <v>-29.225</v>
+        <v>-32.989</v>
       </c>
       <c r="E86" t="n">
-        <v>192.85</v>
+        <v>193.094</v>
       </c>
       <c r="F86" t="n">
-        <v>7.343</v>
+        <v>5.575</v>
       </c>
       <c r="G86" t="n">
-        <v>5.39</v>
+        <v>5.839</v>
       </c>
       <c r="H86" t="n">
-        <v>192.85</v>
+        <v>193.094</v>
       </c>
     </row>
     <row r="87">
@@ -2714,25 +2714,25 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>7500.094</v>
+        <v>7500.08</v>
       </c>
       <c r="C87" t="n">
-        <v>-3.476</v>
+        <v>-5.357</v>
       </c>
       <c r="D87" t="n">
-        <v>29.219</v>
+        <v>32.983</v>
       </c>
       <c r="E87" t="n">
-        <v>186.024</v>
+        <v>187.976</v>
       </c>
       <c r="F87" t="n">
-        <v>-3.475</v>
+        <v>-5.357</v>
       </c>
       <c r="G87" t="n">
-        <v>63.142</v>
+        <v>56.082</v>
       </c>
       <c r="H87" t="n">
-        <v>186.024</v>
+        <v>187.976</v>
       </c>
     </row>
     <row r="88">
@@ -2740,25 +2740,25 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>7601.436</v>
+        <v>7599.129</v>
       </c>
       <c r="C88" t="n">
-        <v>0.482</v>
+        <v>-0.261</v>
       </c>
       <c r="D88" t="n">
-        <v>22.984</v>
+        <v>26.104</v>
       </c>
       <c r="E88" t="n">
-        <v>189.328</v>
+        <v>189.74</v>
       </c>
       <c r="F88" t="n">
-        <v>2.641</v>
+        <v>1.671</v>
       </c>
       <c r="G88" t="n">
-        <v>58.289</v>
+        <v>54.438</v>
       </c>
       <c r="H88" t="n">
-        <v>189.328</v>
+        <v>189.74</v>
       </c>
     </row>
     <row r="89">
@@ -2766,25 +2766,25 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>7697.002</v>
+        <v>7694.844</v>
       </c>
       <c r="C89" t="n">
-        <v>-4.719</v>
+        <v>-5.392</v>
       </c>
       <c r="D89" t="n">
-        <v>17.104</v>
+        <v>19.457</v>
       </c>
       <c r="E89" t="n">
-        <v>187.834</v>
+        <v>188.356</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.768</v>
+        <v>-3.865</v>
       </c>
       <c r="G89" t="n">
-        <v>56.415</v>
+        <v>51.046</v>
       </c>
       <c r="H89" t="n">
-        <v>187.834</v>
+        <v>188.356</v>
       </c>
     </row>
     <row r="90">
@@ -2792,25 +2792,25 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>7793.134</v>
+        <v>7791.553</v>
       </c>
       <c r="C90" t="n">
-        <v>-5.235</v>
+        <v>-5.509</v>
       </c>
       <c r="D90" t="n">
-        <v>11.19</v>
+        <v>12.74</v>
       </c>
       <c r="E90" t="n">
-        <v>188.864</v>
+        <v>187.157</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.632</v>
+        <v>-2.206</v>
       </c>
       <c r="G90" t="n">
-        <v>50.177</v>
+        <v>49.962</v>
       </c>
       <c r="H90" t="n">
-        <v>188.864</v>
+        <v>187.157</v>
       </c>
     </row>
     <row r="91">
@@ -2818,25 +2818,25 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>7889.052</v>
+        <v>7887.281</v>
       </c>
       <c r="C91" t="n">
-        <v>-5.82</v>
+        <v>-6.594</v>
       </c>
       <c r="D91" t="n">
-        <v>5.288</v>
+        <v>6.092</v>
       </c>
       <c r="E91" t="n">
-        <v>190.115</v>
+        <v>188.859</v>
       </c>
       <c r="F91" t="n">
-        <v>1.654</v>
+        <v>-2.206</v>
       </c>
       <c r="G91" t="n">
-        <v>41.2</v>
+        <v>43.318</v>
       </c>
       <c r="H91" t="n">
-        <v>190.115</v>
+        <v>188.859</v>
       </c>
     </row>
     <row r="92">
@@ -2844,25 +2844,25 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>7984.996</v>
+        <v>7983.753</v>
       </c>
       <c r="C92" t="n">
-        <v>-5.636</v>
+        <v>-6.46</v>
       </c>
       <c r="D92" t="n">
-        <v>5.147</v>
+        <v>5.95</v>
       </c>
       <c r="E92" t="n">
-        <v>191.383</v>
+        <v>191.009</v>
       </c>
       <c r="F92" t="n">
-        <v>1.917</v>
+        <v>0.585</v>
       </c>
       <c r="G92" t="n">
-        <v>36.958</v>
+        <v>34.177</v>
       </c>
       <c r="H92" t="n">
-        <v>191.383</v>
+        <v>191.009</v>
       </c>
     </row>
     <row r="93">
@@ -2870,25 +2870,25 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>8081.018</v>
+        <v>8079.822</v>
       </c>
       <c r="C93" t="n">
-        <v>-3.872</v>
+        <v>-4.985</v>
       </c>
       <c r="D93" t="n">
-        <v>3.793</v>
+        <v>4.389</v>
       </c>
       <c r="E93" t="n">
-        <v>191.85</v>
+        <v>192.238</v>
       </c>
       <c r="F93" t="n">
-        <v>2.413</v>
+        <v>1.182</v>
       </c>
       <c r="G93" t="n">
-        <v>30.737</v>
+        <v>27.368</v>
       </c>
       <c r="H93" t="n">
-        <v>191.85</v>
+        <v>192.238</v>
       </c>
     </row>
     <row r="94">
@@ -2896,25 +2896,25 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>8179.93</v>
+        <v>8175.948</v>
       </c>
       <c r="C94" t="n">
-        <v>-2.055</v>
+        <v>-3.509</v>
       </c>
       <c r="D94" t="n">
-        <v>2.398</v>
+        <v>2.828</v>
       </c>
       <c r="E94" t="n">
-        <v>193.747</v>
+        <v>193.496</v>
       </c>
       <c r="F94" t="n">
-        <v>3.213</v>
+        <v>2.048</v>
       </c>
       <c r="G94" t="n">
-        <v>23.173</v>
+        <v>21.992</v>
       </c>
       <c r="H94" t="n">
-        <v>193.747</v>
+        <v>193.496</v>
       </c>
     </row>
     <row r="95">
@@ -2922,25 +2922,25 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>8289.099</v>
+        <v>8272.383</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.049</v>
+        <v>-2.029</v>
       </c>
       <c r="D95" t="n">
-        <v>0.859</v>
+        <v>1.261</v>
       </c>
       <c r="E95" t="n">
-        <v>194.127</v>
+        <v>194.786</v>
       </c>
       <c r="F95" t="n">
-        <v>5.44</v>
+        <v>2.85</v>
       </c>
       <c r="G95" t="n">
-        <v>20.675</v>
+        <v>16.829</v>
       </c>
       <c r="H95" t="n">
-        <v>194.127</v>
+        <v>194.786</v>
       </c>
     </row>
     <row r="96">
@@ -2948,25 +2948,25 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>8385.204</v>
+        <v>8368.339</v>
       </c>
       <c r="C96" t="n">
-        <v>0.044</v>
+        <v>-1.978</v>
       </c>
       <c r="D96" t="n">
-        <v>0.788</v>
+        <v>1.207</v>
       </c>
       <c r="E96" t="n">
-        <v>194.181</v>
+        <v>195.473</v>
       </c>
       <c r="F96" t="n">
-        <v>8.550000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="G96" t="n">
-        <v>16.317</v>
+        <v>13.84</v>
       </c>
       <c r="H96" t="n">
-        <v>194.181</v>
+        <v>195.473</v>
       </c>
     </row>
     <row r="97">
@@ -2974,25 +2974,25 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>8481.017</v>
+        <v>8466.887000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>0.296</v>
+        <v>-1.701</v>
       </c>
       <c r="D97" t="n">
-        <v>0.594</v>
+        <v>0.914</v>
       </c>
       <c r="E97" t="n">
-        <v>194.292</v>
+        <v>195.32</v>
       </c>
       <c r="F97" t="n">
-        <v>10.631</v>
+        <v>1.301</v>
       </c>
       <c r="G97" t="n">
-        <v>13.532</v>
+        <v>11.906</v>
       </c>
       <c r="H97" t="n">
-        <v>194.292</v>
+        <v>195.32</v>
       </c>
     </row>
     <row r="98">
@@ -3000,25 +3000,25 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>8577.138999999999</v>
+        <v>8579.534</v>
       </c>
       <c r="C98" t="n">
-        <v>0.549</v>
+        <v>-1.385</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="E98" t="n">
-        <v>194.436</v>
+        <v>195.263</v>
       </c>
       <c r="F98" t="n">
-        <v>12.788</v>
+        <v>1.944</v>
       </c>
       <c r="G98" t="n">
-        <v>11.139</v>
+        <v>11.927</v>
       </c>
       <c r="H98" t="n">
-        <v>194.436</v>
+        <v>195.263</v>
       </c>
     </row>
     <row r="99">
@@ -3026,25 +3026,25 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>8672.971</v>
+        <v>8688.874</v>
       </c>
       <c r="C99" t="n">
-        <v>0.801</v>
+        <v>-1.079</v>
       </c>
       <c r="D99" t="n">
-        <v>0.206</v>
+        <v>0.256</v>
       </c>
       <c r="E99" t="n">
-        <v>194.32</v>
+        <v>194.592</v>
       </c>
       <c r="F99" t="n">
-        <v>10.241</v>
+        <v>4.647</v>
       </c>
       <c r="G99" t="n">
-        <v>8.497</v>
+        <v>12.111</v>
       </c>
       <c r="H99" t="n">
-        <v>194.32</v>
+        <v>194.592</v>
       </c>
     </row>
     <row r="100">
@@ -3052,25 +3052,25 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>8769.309999999999</v>
+        <v>8785.280999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>1.055</v>
+        <v>-0.439</v>
       </c>
       <c r="D100" t="n">
-        <v>0.012</v>
+        <v>1.38</v>
       </c>
       <c r="E100" t="n">
-        <v>194.729</v>
+        <v>194.118</v>
       </c>
       <c r="F100" t="n">
-        <v>7.816</v>
+        <v>5.209</v>
       </c>
       <c r="G100" t="n">
-        <v>2.802</v>
+        <v>12.284</v>
       </c>
       <c r="H100" t="n">
-        <v>194.729</v>
+        <v>194.118</v>
       </c>
     </row>
     <row r="101">
@@ -3078,25 +3078,25 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>8865.339</v>
+        <v>8881.619999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>6.618</v>
+        <v>5.562</v>
       </c>
       <c r="D101" t="n">
-        <v>9.903</v>
+        <v>11.909</v>
       </c>
       <c r="E101" t="n">
-        <v>194.579</v>
+        <v>193.814</v>
       </c>
       <c r="F101" t="n">
-        <v>7.814</v>
+        <v>5.632</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.354</v>
+        <v>9.632</v>
       </c>
       <c r="H101" t="n">
-        <v>194.579</v>
+        <v>193.814</v>
       </c>
     </row>
     <row r="102">
@@ -3104,25 +3104,25 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>8961.071</v>
+        <v>8977.794</v>
       </c>
       <c r="C102" t="n">
-        <v>12.514</v>
+        <v>11.552</v>
       </c>
       <c r="D102" t="n">
-        <v>20.384</v>
+        <v>22.42</v>
       </c>
       <c r="E102" t="n">
-        <v>193.923</v>
+        <v>193.213</v>
       </c>
       <c r="F102" t="n">
-        <v>7.456</v>
+        <v>5.606</v>
       </c>
       <c r="G102" t="n">
-        <v>1.238</v>
+        <v>11.872</v>
       </c>
       <c r="H102" t="n">
-        <v>193.923</v>
+        <v>193.213</v>
       </c>
     </row>
     <row r="103">
@@ -3130,25 +3130,25 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>9057.206</v>
+        <v>9073.98</v>
       </c>
       <c r="C103" t="n">
-        <v>18.435</v>
+        <v>17.542</v>
       </c>
       <c r="D103" t="n">
-        <v>30.909</v>
+        <v>32.932</v>
       </c>
       <c r="E103" t="n">
-        <v>192.808</v>
+        <v>192.146</v>
       </c>
       <c r="F103" t="n">
-        <v>6.488</v>
+        <v>7.401</v>
       </c>
       <c r="G103" t="n">
-        <v>8.129</v>
+        <v>13.436</v>
       </c>
       <c r="H103" t="n">
-        <v>192.808</v>
+        <v>192.146</v>
       </c>
     </row>
   </sheetData>
